--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -456,7 +456,7 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C3" t="str">
         <v>C. VANIGLIA</v>
@@ -468,7 +468,7 @@
         <v>C. LATTE</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
@@ -508,7 +508,7 @@
         <v>C. ZENZERO</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="str">
         <v>C. MADAGASCAR</v>
@@ -528,7 +528,7 @@
         <v>BIANCANEVE</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>C. CANNELLA</v>
@@ -540,7 +540,7 @@
         <v>C. VENEZUELA</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="str">
         <v>ANGURIA</v>
@@ -572,7 +572,7 @@
         <v>AVOCADO E LIME</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -666,7 +666,7 @@
         <v>FIORDILATTE</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
@@ -741,7 +741,7 @@
         <v>FRUTTI BOSCO</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -755,7 +755,7 @@
         <v>C. ESTASY</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="str">
         <v>LAMPONE</v>
@@ -809,7 +809,7 @@
         <v>NOCCIOLA</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="str">
         <v>NOCCIOLATA</v>
@@ -818,7 +818,7 @@
         <v>P. VEGAN</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="str">
         <v>MANGO</v>
@@ -844,7 +844,7 @@
         <v>MELA N. E C.</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -878,7 +878,7 @@
         <v>LAVANDA</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="str">
         <v>SUSHI GELATO</v>
@@ -966,7 +966,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="str">
         <v>PANETTONE</v>
@@ -1018,7 +1018,7 @@
         <v>PISTACCHI</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="str">
         <v>PICCHIE</v>
@@ -1044,7 +1044,7 @@
         <v>PESCA AL VINO</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1069,7 +1069,7 @@
         <v>STRIA</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="str">
         <v>COPP. GRANDI</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -886,6 +886,9 @@
       <c r="G22" t="str">
         <v>MIRTILLO</v>
       </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1017,9 +1020,6 @@
       <c r="C29" t="str">
         <v>PISTACCHI</v>
       </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
       <c r="E29" t="str">
         <v>PICCHIE</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>PERA GORGONZOLA</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1068,9 +1068,6 @@
       <c r="A32" t="str">
         <v>STRIA</v>
       </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
       <c r="E32" t="str">
         <v>COPP. GRANDI</v>
       </c>
@@ -1097,7 +1094,7 @@
         <v>ZUCCA E SEMI</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Flavors" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,46 +397,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Flavor 1</v>
+        <v>Gelato</v>
       </c>
       <c r="B1" t="str">
-        <v>Qty 1</v>
+        <v>ORDINE</v>
       </c>
       <c r="C1" t="str">
-        <v>Flavor 2</v>
+        <v>Creme</v>
       </c>
       <c r="D1" t="str">
-        <v>Qty 2</v>
+        <v>ORDINE</v>
       </c>
       <c r="E1" t="str">
-        <v>Flavor 3</v>
+        <v>Cioccolati</v>
       </c>
       <c r="F1" t="str">
-        <v>Qty 3</v>
+        <v>ORDINE</v>
       </c>
       <c r="G1" t="str">
-        <v>Flavor 4</v>
+        <v>Sorbetti</v>
       </c>
       <c r="H1" t="str">
-        <v>Qty 4</v>
+        <v>ORDINE</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ARACHIDI</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="str">
-        <v>CREMA</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
@@ -456,16 +453,16 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="str">
-        <v>C. VANIGLIA</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>C. LATTE</v>
+        <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -479,71 +476,68 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BAKLAVA</v>
+        <v>BASILICO NOCI E MIELE</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
       </c>
       <c r="C4" t="str">
-        <v>C. FRAGOLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="str">
-        <v>C. KENTUCKY</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>AMARENA E BIRRA</v>
+        <v>ANANAS E ZENZERO</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BASILICO NOCI E MELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
-        <v>C. ZENZERO</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
-        <v>C. MADAGASCAR</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="G5" t="str">
-        <v>ANANAS E ZENZ.</v>
+        <v>ANGURIA</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BIANCANEVE</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C6" t="str">
-        <v>C. CANNELLA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>C. VENEZUELA</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
+        <v>CIOCCOLATO BIANCO</v>
       </c>
       <c r="G6" t="str">
-        <v>ANGURIA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -551,25 +545,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CAFFÈ</v>
+        <v>CAFFE'</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" t="str">
+        <v>CREMA FRAGOLE E MANDORLE</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="C7" t="str">
-        <v>C. AGNESE</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7" t="str">
-        <v>C. PIMENTO</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7" t="str">
-        <v>AVOCADO E LIME</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -577,85 +571,82 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CIOCC. BIANCO</v>
+        <v>COCCO CREMA</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>C. LEMON CURD</v>
+        <v>CREMA PASTICCIERA PARISI</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="str">
-        <v>C. LAPSANG</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>BANANA E LIME</v>
+        <v>CACHI</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>COCCO CREMA</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
+        <v>CREMA BANANA E CROCCANTE AL SESAMO</v>
       </c>
       <c r="C9" t="str">
-        <v>CHEESE MIRT</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="str">
-        <v>C. WASABY</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>CIOCCOLATO EQUADOR</v>
       </c>
       <c r="G9" t="str">
-        <v>CACHI</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>CILIEGIA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>C. BANANA</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
+        <v>FICHI ALLA GRECA</v>
       </c>
       <c r="C10" t="str">
-        <v>CARROT LAKE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
       </c>
       <c r="E10" t="str">
-        <v>C. ROSEMARY</v>
+        <v>CIOCCOLATO KENTUCKY</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>CASTAGNA</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>COCCO</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FINOCCHIO</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="C11" t="str">
-        <v>TIRAMISU</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="str">
-        <v>C. PORCELLANA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
       </c>
       <c r="G11" t="str">
         <v>COCCO AL RUM</v>
@@ -675,110 +666,101 @@
         <v>2</v>
       </c>
       <c r="E12" t="str">
-        <v>C. AMBOA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v>FICHI</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
       </c>
       <c r="C13" t="str">
-        <v>ZABAIONE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="str">
-        <v>GIANDUIA</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="G13" t="str">
-        <v>FRAGOLA</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MENTA CIOCC.</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
+        <v>LATTE &amp; CEREALI</v>
       </c>
       <c r="C14" t="str">
-        <v>Z. MOSCATO</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="str">
-        <v>C. ARANCIA</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
+        <v>CIOCCOLATO UGANDA</v>
       </c>
       <c r="G14" t="str">
-        <v>FRAG. CALVADOS</v>
+        <v>FEIJOA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>M. BIANCA</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Z. RATAFIA</v>
+        <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
       <c r="E15" t="str">
-        <v>C. FRUTTOSIO</v>
+        <v>CIOCCOLATO VENEZUELA</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
       </c>
       <c r="G15" t="str">
-        <v>FRUTTI BOSCO</v>
-      </c>
-      <c r="H15">
-        <v>3</v>
+        <v>FICHI</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>M. TOSTATA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
       </c>
       <c r="C16" t="str">
-        <v>Z. FATA</v>
+        <v>speciali</v>
       </c>
       <c r="E16" t="str">
-        <v>C. ESTASY</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>LAMPONE</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
+        <v>FICHI D INDIA</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>M. ARANCIA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17" t="str">
-        <v>Z. ZIBIBBO</v>
+        <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
       </c>
       <c r="E17" t="str">
-        <v>N. FRUTTOSIO</v>
+        <v>ESTASI</v>
       </c>
       <c r="G17" t="str">
-        <v>LIMONE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -786,125 +768,110 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>M. CARDAMOMO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>SACHER</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
+        <v>CASTAGNACCIO</v>
       </c>
       <c r="E18" t="str">
-        <v>V. GIANDUIA</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="G18" t="str">
-        <v>MANDARINO</v>
+        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="str">
-        <v>NOCCIOLATA</v>
+        <v>COTOGNATA</v>
       </c>
       <c r="E19" t="str">
-        <v>P. VEGAN</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="G19" t="str">
-        <v>MANGO</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>NOCI E UVETTA</v>
+        <v>MANDORLA E ARANCIA</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
       </c>
       <c r="C20" t="str">
-        <v>LA-LA-</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
+        <v>CREMA COGNAC E NOCE MOSCATA</v>
       </c>
       <c r="E20" t="str">
-        <v>COPPA</v>
+        <v>GIANDUIA VARIEGATA</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>MELA N. E C.</v>
-      </c>
-      <c r="H20">
-        <v>2</v>
+        <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PERE BH</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C21" t="str">
-        <v>STRACCHINO</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
+        <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
       </c>
       <c r="E21" t="str">
-        <v>CIALDINE</v>
+        <v>MOU LATTE SALATO</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>MELONE</v>
+        <v>HIBISCUS</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>POLLICINA</v>
+        <v>MONTBLANC</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v>LAVANDA</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
+        <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
       </c>
       <c r="E22" t="str">
-        <v>SUSHI GELATO</v>
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>MIRTILLO</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>BRONTE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C23" t="str">
-        <v>NOCE BURRO</v>
-      </c>
-      <c r="E23" t="str">
-        <v>SUSHI TIRAMISU</v>
+        <v>FIORI DI MAGNOLIA &amp; LIME</v>
       </c>
       <c r="G23" t="str">
-        <v>MORA</v>
+        <v>LIMONE</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -912,36 +879,30 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>RICOTTA AGRUMI</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C24" t="str">
-        <v>FIORDIFIOR</v>
+        <v>GELATO DI PANETTONE</v>
       </c>
       <c r="E24" t="str">
-        <v>SUSHI MISTI</v>
+        <v>Varie</v>
       </c>
       <c r="G24" t="str">
-        <v>PANACEA</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
+        <v>MANDARINO</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>RICOTTA COCCO</v>
+        <v>NOCI E UVETTA DI CORINTO</v>
       </c>
       <c r="C25" t="str">
-        <v>PAMPANELLA</v>
+        <v>GELSI BIANCHI, SAKE' E ANACARDI SALATI</v>
       </c>
       <c r="E25" t="str">
-        <v>T.S. 6P</v>
+        <v>CAPRESE</v>
       </c>
       <c r="G25" t="str">
-        <v>PASSION</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -949,158 +910,351 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>RISO E VANIGLIA</v>
-      </c>
-      <c r="B26">
+        <v>NOCI PECAN</v>
+      </c>
+      <c r="C26" t="str">
+        <v>GORGONZOLA</v>
+      </c>
+      <c r="E26" t="str">
+        <v>CHICCHIAINI</v>
+      </c>
+      <c r="G26" t="str">
+        <v>MELA MANDORLA E CANNELLA</v>
+      </c>
+      <c r="H26">
         <v>1</v>
-      </c>
-      <c r="C26" t="str">
-        <v>TORRONE</v>
-      </c>
-      <c r="E26" t="str">
-        <v>T.S. 8P</v>
-      </c>
-      <c r="G26" t="str">
-        <v>PAPAYA</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C27" t="str">
-        <v>PANETTONE</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
+        <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
       </c>
       <c r="E27" t="str">
-        <v>T.G. 6P</v>
+        <v>CIALDINE</v>
       </c>
       <c r="G27" t="str">
-        <v>PENSIERO</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SEADAS</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C28" t="str">
-        <v>MONTBLANC</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
+        <v>MATE-LATE</v>
       </c>
       <c r="E28" t="str">
-        <v>T.G. 8P</v>
+        <v>CIOCCOLATA CALDA</v>
       </c>
       <c r="G28" t="str">
-        <v>PERA</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
+        <v>MELONE</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>YOGURT</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" t="str">
+        <v>MOJITO ALLA AMARENA</v>
+      </c>
+      <c r="E29" t="str">
+        <v>COPPA IN CIALDA</v>
+      </c>
+      <c r="G29" t="str">
+        <v>MIRTILLO</v>
+      </c>
+      <c r="H29">
         <v>2</v>
-      </c>
-      <c r="C29" t="str">
-        <v>PISTACCHI</v>
-      </c>
-      <c r="E29" t="str">
-        <v>PICCHIE</v>
-      </c>
-      <c r="G29" t="str">
-        <v>PERA GORGONZOLA</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>VENERE</v>
+        <v>POLLICINA</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
       </c>
       <c r="C30" t="str">
-        <v>RICE COCCO</v>
+        <v>NON TI SCORDAR DI ME</v>
       </c>
       <c r="E30" t="str">
-        <v>HUMA</v>
+        <v>COPPETTA GRANDE</v>
       </c>
       <c r="G30" t="str">
-        <v>PESCA AL VINO</v>
+        <v>MORA</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>THE VERDE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="str">
-        <v>LIM/MAS</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="E31" t="str">
-        <v>COPP. PICCOLE</v>
+        <v>COPPETTA PICCOLA</v>
       </c>
       <c r="G31" t="str">
-        <v>PUNCH</v>
+        <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>STRIA</v>
+        <v>RICOTTA E FICHI ALLA GRECA</v>
+      </c>
+      <c r="C32" t="str">
+        <v>PECORINO</v>
       </c>
       <c r="E32" t="str">
-        <v>COPP. GRANDI</v>
+        <v>MOUSSE</v>
       </c>
       <c r="G32" t="str">
-        <v>UVA NOCI</v>
+        <v>PAPAYA</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33" t="str">
+        <v>PERA AL GORGONZOLA</v>
+      </c>
       <c r="E33" t="str">
-        <v>CAPRESE</v>
+        <v>SUSHI GELATO</v>
       </c>
       <c r="G33" t="str">
-        <v>UVA FRAGOLA</v>
+        <v>PASSION FRUIT</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="str">
+        <v>RICOTTA, AMARENE &amp; NOCCIOLE PRALINATE</v>
+      </c>
+      <c r="C34" t="str">
+        <v>PERA E PECORINO DOP</v>
+      </c>
       <c r="E34" t="str">
-        <v>C. CALDA</v>
-      </c>
-      <c r="F34">
+        <v>SUSHI MISTI</v>
+      </c>
+      <c r="G34" t="str">
+        <v>PENSIERO</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>RICOTTA, MIELE E COCCO</v>
+      </c>
+      <c r="C35" t="str">
+        <v>PESCA BIANCA AL BASILICO</v>
+      </c>
+      <c r="E35" t="str">
+        <v>SUSHI TIRAMISU</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PERA</v>
+      </c>
+      <c r="H35">
         <v>2</v>
       </c>
-      <c r="G34" t="str">
-        <v>ZUCCA E SEMI</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>RISO E VANIGLIA</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36" t="str">
+        <v>PESCA TABACCHIERA</v>
+      </c>
+      <c r="E36" t="str">
+        <v>TORTA AGNESE 6P</v>
+      </c>
+      <c r="G36" t="str">
+        <v>PESCHE AL VINO</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SEADAS</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="str">
+        <v>POMODORO DATTERINO</v>
+      </c>
+      <c r="E37" t="str">
+        <v>TORTA AGNESE 8P</v>
+      </c>
+      <c r="G37" t="str">
+        <v>PRUGNA ROSSA, FIORI D'IBISCO</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+      </c>
+      <c r="C38" t="str">
+        <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
+      </c>
+      <c r="E38" t="str">
+        <v>TORTA CHEESCAKE 6P</v>
+      </c>
+      <c r="G38" t="str">
+        <v>PRUGNE AL SAKE'</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ROSA KAEKADE E ARANCIA</v>
+      </c>
+      <c r="E39" t="str">
+        <v>TORTA CHEESCAKE 8P</v>
+      </c>
+      <c r="G39" t="str">
+        <v>PUNCH PARADISE</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>STRACCIATELLA</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="str">
+        <v>STRACCIATELLA AL FIOR DI RISO</v>
+      </c>
+      <c r="E40" t="str">
+        <v>TORTA LAURA 6P</v>
+      </c>
+      <c r="G40" t="str">
+        <v>RIBES NERO</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TE VERDE MATCHA</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41" t="str">
+        <v>TORRONE SALATO</v>
+      </c>
+      <c r="E41" t="str">
+        <v>TORTA LAURA 8P</v>
+      </c>
+      <c r="G41" t="str">
+        <v>UVA E NOCI</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>VENERE ROSA</v>
+      </c>
+      <c r="C42" t="str">
+        <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>TORTA TIRAMISU 6P</v>
+      </c>
+      <c r="G42" t="str">
+        <v>UVA FRAGOLA E ZENZERO</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>YOGURT</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
+      </c>
+      <c r="E43" t="str">
+        <v>TORTA TIRAMISU 8P</v>
+      </c>
+      <c r="G43" t="str">
+        <v>V. BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" t="str">
+        <v>V. CASTAGNA AL WHISKY</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" t="str">
+        <v>V. CASTAGNA E MIRTO</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" t="str">
+        <v>V. EVERGREEN BRONTE VEGAN</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" t="str">
+        <v>V. NOCCIOLA AL FRUTTOSIO</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" t="str">
+        <v>ZUCCA COI SUOI SEMI CARAMELLATI</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Flavors" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -397,31 +397,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:P48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Gelato</v>
       </c>
       <c r="B1" t="str">
-        <v>ORDINE</v>
+        <v>ESAURITO</v>
       </c>
       <c r="C1" t="str">
-        <v>Creme</v>
+        <v>MANTENIMENTO</v>
       </c>
       <c r="D1" t="str">
         <v>ORDINE</v>
       </c>
       <c r="E1" t="str">
+        <v>Creme</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ESAURITO</v>
+      </c>
+      <c r="G1" t="str">
+        <v>MANTENIMENTO</v>
+      </c>
+      <c r="H1" t="str">
+        <v>ORDINE</v>
+      </c>
+      <c r="I1" t="str">
         <v>Cioccolati</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
+        <v>ESAURITO</v>
+      </c>
+      <c r="K1" t="str">
+        <v>MANTENIMENTO</v>
+      </c>
+      <c r="L1" t="str">
         <v>ORDINE</v>
       </c>
-      <c r="G1" t="str">
+      <c r="M1" t="str">
         <v>Sorbetti</v>
       </c>
-      <c r="H1" t="str">
+      <c r="N1" t="str">
+        <v>ESAURITO</v>
+      </c>
+      <c r="O1" t="str">
+        <v>MANTENIMENTO</v>
+      </c>
+      <c r="P1" t="str">
         <v>ORDINE</v>
       </c>
     </row>
@@ -429,74 +453,149 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="str">
         <v>CIOCCOLATO</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="str">
         <v>ALBICOCCA</v>
       </c>
-      <c r="H2">
-        <v>2</v>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>BACIO DEL PRINCIPE</v>
       </c>
-      <c r="B3">
-        <v>4</v>
+      <c r="B3" t="str">
+        <v/>
       </c>
       <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3">
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="E3" t="str">
+      <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3" t="str">
         <v>AMARENA</v>
       </c>
-      <c r="H3">
-        <v>1</v>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="str">
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
       </c>
-      <c r="H4">
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4">
         <v>2</v>
       </c>
     </row>
@@ -504,359 +603,899 @@
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
       </c>
-      <c r="G5" t="str">
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5">
-        <v>0</v>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>BUONGIORNO AMORE</v>
       </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
       <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
       </c>
-      <c r="G6" t="str">
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
-      <c r="H6">
-        <v>0</v>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7">
-        <v>0</v>
+      <c r="B7" t="str">
+        <v/>
       </c>
       <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
-      <c r="F7">
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7">
         <v>2</v>
       </c>
-      <c r="G7" t="str">
+      <c r="M7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7">
-        <v>0</v>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8">
-        <v>1</v>
+      <c r="B8" t="str">
+        <v/>
       </c>
       <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="str">
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="str">
         <v>CACHI</v>
       </c>
-      <c r="H8">
-        <v>0</v>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>CREMA BANANA E CROCCANTE AL SESAMO</v>
       </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
       <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
         <v>CREMA VANIGLIA</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="str">
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
       </c>
-      <c r="G9" t="str">
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>CILIEGIA</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>FICHI ALLA GRECA</v>
       </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
       <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
         <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10" t="str">
         <v>COCCO</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
       <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
         <v>LEMON CURD</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="str">
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>COCCO AL RUM</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12">
-        <v>1</v>
+      <c r="B12" t="str">
+        <v/>
       </c>
       <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12">
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
         <v>2</v>
       </c>
-      <c r="E12" t="str">
+      <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="str">
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13">
-        <v>0</v>
+      <c r="B13" t="str">
+        <v/>
       </c>
       <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
       </c>
-      <c r="G13" t="str">
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
         <v>LATTE &amp; CEREALI</v>
       </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
       <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
         <v>ZABAIONE GELATO</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" t="str">
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
         <v>CIOCCOLATO UGANDA</v>
       </c>
-      <c r="G14" t="str">
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>FEIJOA</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>LATTE DI FICO (PAMPANELLA)</v>
       </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15" t="str">
         <v>FICHI</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="str">
+        <v/>
       </c>
       <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
         <v>speciali</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
         <v>CIOCCOLATO WASABI</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" t="str">
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>FICHI D INDIA</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v>LIQUIRIZIA</v>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="str">
+        <v/>
       </c>
       <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="G17" t="str">
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17" t="str">
         <v>FRAGOLA</v>
       </c>
-      <c r="H17">
-        <v>0</v>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
-      <c r="B18">
-        <v>1</v>
+      <c r="B18" t="str">
+        <v/>
       </c>
       <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
       </c>
-      <c r="E18" t="str">
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="G18" t="str">
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>MANDORLA BIANCA</v>
       </c>
-      <c r="B19">
-        <v>1</v>
+      <c r="B19" t="str">
+        <v/>
       </c>
       <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
         <v>COTOGNATA</v>
       </c>
-      <c r="E19" t="str">
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>GIANDUIA</v>
       </c>
-      <c r="G19" t="str">
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20">
-        <v>0</v>
+      <c r="B20" t="str">
+        <v/>
       </c>
       <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>GIANDUIA VARIEGATA</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
       <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
       </c>
-      <c r="E21" t="str">
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>MOU LATTE SALATO</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="str">
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>HIBISCUS</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v>MONTBLANC</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22">
         <v>2</v>
       </c>
-      <c r="C22" t="str">
+      <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
       </c>
-      <c r="E22" t="str">
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
         <v>SACHER TORTE</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22">
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22">
         <v>1</v>
       </c>
     </row>
@@ -864,64 +1503,199 @@
       <c r="A23" t="str">
         <v>NOCCIOLA</v>
       </c>
-      <c r="B23">
-        <v>0</v>
+      <c r="B23" t="str">
+        <v/>
       </c>
       <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
       </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
       <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
         <v>LIMONE</v>
       </c>
-      <c r="H23">
-        <v>0</v>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
       <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
       </c>
-      <c r="E24" t="str">
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
         <v>Varie</v>
       </c>
-      <c r="G24" t="str">
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
         <v>MANDARINO</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
         <v>NOCI E UVETTA DI CORINTO</v>
       </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
       <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
         <v>GELSI BIANCHI, SAKE' E ANACARDI SALATI</v>
       </c>
-      <c r="E25" t="str">
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
         <v>CAPRESE</v>
       </c>
-      <c r="G25" t="str">
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25">
-        <v>0</v>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v>NOCI PECAN</v>
       </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
       <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
         <v>GORGONZOLA</v>
       </c>
-      <c r="E26" t="str">
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
         <v>CHICCHIAINI</v>
       </c>
-      <c r="G26" t="str">
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
-      <c r="H26">
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26">
         <v>1</v>
       </c>
     </row>
@@ -929,53 +1703,149 @@
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27">
-        <v>0</v>
+      <c r="B27" t="str">
+        <v/>
       </c>
       <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
       </c>
-      <c r="E27" t="str">
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
         <v>CIALDINE</v>
       </c>
-      <c r="G27" t="str">
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
         <v>MELOGRANO WONDERFUL</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v>PISTACCHIO DI BRONTE</v>
       </c>
-      <c r="B28">
-        <v>7</v>
+      <c r="B28" t="str">
+        <v/>
       </c>
       <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" t="str">
         <v>MATE-LATE</v>
       </c>
-      <c r="E28" t="str">
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
         <v>CIOCCOLATA CALDA</v>
       </c>
-      <c r="G28" t="str">
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
         <v>MELONE</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v>PISTACCHIO SIRIANO</v>
       </c>
-      <c r="B29">
-        <v>0</v>
+      <c r="B29" t="str">
+        <v/>
       </c>
       <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
       </c>
-      <c r="E29" t="str">
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
         <v>COPPA IN CIALDA</v>
       </c>
-      <c r="G29" t="str">
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29">
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29">
         <v>2</v>
       </c>
     </row>
@@ -983,110 +1853,299 @@
       <c r="A30" t="str">
         <v>POLLICINA</v>
       </c>
-      <c r="B30">
-        <v>0</v>
+      <c r="B30" t="str">
+        <v/>
       </c>
       <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
       </c>
-      <c r="E30" t="str">
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
         <v>COPPETTA GRANDE</v>
       </c>
-      <c r="G30" t="str">
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30">
-        <v>0</v>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>RICOTTA E AGRUMI</v>
       </c>
-      <c r="B31">
-        <v>1</v>
+      <c r="B31" t="str">
+        <v/>
       </c>
       <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
       </c>
-      <c r="E31" t="str">
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
         <v>COPPETTA PICCOLA</v>
       </c>
-      <c r="G31" t="str">
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31">
-        <v>0</v>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v>RICOTTA E FICHI ALLA GRECA</v>
       </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
       <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
         <v>PECORINO</v>
       </c>
-      <c r="E32" t="str">
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
         <v>MOUSSE</v>
       </c>
-      <c r="G32" t="str">
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
         <v>PAPAYA</v>
       </c>
-      <c r="H32">
-        <v>0</v>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33">
-        <v>0</v>
+      <c r="B33" t="str">
+        <v/>
       </c>
       <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
       </c>
-      <c r="E33" t="str">
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
         <v>SUSHI GELATO</v>
       </c>
-      <c r="G33" t="str">
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33">
-        <v>0</v>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v>RICOTTA, AMARENE &amp; NOCCIOLE PRALINATE</v>
       </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
       <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
         <v>PERA E PECORINO DOP</v>
       </c>
-      <c r="E34" t="str">
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
         <v>SUSHI MISTI</v>
       </c>
-      <c r="G34" t="str">
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
         <v>PENSIERO</v>
       </c>
-      <c r="H34">
-        <v>0</v>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
       <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
       </c>
-      <c r="E35" t="str">
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
         <v>SUSHI TIRAMISU</v>
       </c>
-      <c r="G35" t="str">
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
         <v>PERA</v>
       </c>
-      <c r="H35">
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35">
         <v>2</v>
       </c>
     </row>
@@ -1094,19 +2153,49 @@
       <c r="A36" t="str">
         <v>RISO E VANIGLIA</v>
       </c>
-      <c r="B36">
-        <v>0</v>
+      <c r="B36" t="str">
+        <v/>
       </c>
       <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
       </c>
-      <c r="E36" t="str">
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
         <v>TORTA AGNESE 6P</v>
       </c>
-      <c r="G36" t="str">
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36">
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36">
         <v>2</v>
       </c>
     </row>
@@ -1114,147 +2203,605 @@
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37">
         <v>2</v>
       </c>
-      <c r="C37" t="str">
+      <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
       </c>
-      <c r="E37" t="str">
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
         <v>TORTA AGNESE 8P</v>
       </c>
-      <c r="G37" t="str">
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
         <v>PRUGNA ROSSA, FIORI D'IBISCO</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
       <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="str">
         <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
       </c>
-      <c r="E38" t="str">
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
         <v>TORTA CHEESCAKE 6P</v>
       </c>
-      <c r="G38" t="str">
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
         <v>PRUGNE AL SAKE'</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
-      <c r="B39">
-        <v>2</v>
+      <c r="B39" t="str">
+        <v/>
       </c>
       <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
       </c>
-      <c r="E39" t="str">
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
         <v>TORTA CHEESCAKE 8P</v>
       </c>
-      <c r="G39" t="str">
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
         <v>PUNCH PARADISE</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v>STRACCIATELLA</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40">
         <v>4</v>
       </c>
-      <c r="C40" t="str">
+      <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
       </c>
-      <c r="E40" t="str">
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
         <v>TORTA LAURA 6P</v>
       </c>
-      <c r="G40" t="str">
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
         <v>RIBES NERO</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v>TE VERDE MATCHA</v>
       </c>
-      <c r="B41">
-        <v>0</v>
+      <c r="B41" t="str">
+        <v/>
       </c>
       <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
         <v>TORRONE SALATO</v>
       </c>
-      <c r="E41" t="str">
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
         <v>TORTA LAURA 8P</v>
       </c>
-      <c r="G41" t="str">
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
         <v>UVA E NOCI</v>
       </c>
-      <c r="H41">
-        <v>0</v>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v>VENERE ROSA</v>
       </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
       <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
       </c>
-      <c r="E42" t="str">
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
         <v>TORTA TIRAMISU 6P</v>
       </c>
-      <c r="G42" t="str">
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
         <v>UVA FRAGOLA E ZENZERO</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v>YOGURT</v>
       </c>
-      <c r="B43">
-        <v>3</v>
+      <c r="B43" t="str">
+        <v/>
       </c>
       <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
       </c>
-      <c r="E43" t="str">
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
         <v>TORTA TIRAMISU 8P</v>
       </c>
-      <c r="G43" t="str">
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
         <v>V. BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
+      <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
       <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
         <v>V. CASTAGNA AL WHISKY</v>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
       <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
         <v>V. CASTAGNA E MIRTO</v>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
       <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
         <v>V. EVERGREEN BRONTE VEGAN</v>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
       <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
         <v>V. NOCCIOLA AL FRUTTOSIO</v>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
+      <c r="A48" t="str">
+        <v/>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
       <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
         <v>ZUCCA COI SUOI SEMI CARAMELLATI</v>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -459,8 +459,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -471,8 +471,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -484,7 +484,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -495,8 +495,8 @@
       <c r="O2" t="str">
         <v/>
       </c>
-      <c r="P2">
-        <v>1</v>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -545,8 +545,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
-        <v/>
+      <c r="P3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -559,8 +559,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>3</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -596,7 +596,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -645,8 +645,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -659,8 +659,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -695,8 +695,8 @@
       <c r="O6" t="str">
         <v/>
       </c>
-      <c r="P6" t="str">
-        <v/>
+      <c r="P6">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -721,8 +721,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -734,7 +734,7 @@
         <v/>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -745,8 +745,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -759,8 +759,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>1</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -771,8 +771,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -783,8 +783,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8">
-        <v>1</v>
+      <c r="L8" t="str">
+        <v/>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -795,8 +795,8 @@
       <c r="O8" t="str">
         <v/>
       </c>
-      <c r="P8" t="str">
-        <v/>
+      <c r="P8">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -821,8 +821,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -871,8 +871,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>2</v>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -909,8 +909,8 @@
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11" t="str">
-        <v/>
+      <c r="D11">
+        <v>1</v>
       </c>
       <c r="E11" t="str">
         <v>LEMON CURD</v>
@@ -959,8 +959,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -971,8 +971,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12">
-        <v>2</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -1021,8 +1021,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>2</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1072,7 +1072,7 @@
         <v/>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="str">
         <v>CIOCCOLATO UGANDA</v>
@@ -1209,8 +1209,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17" t="str">
-        <v/>
+      <c r="D17">
+        <v>2</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>1</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1245,8 +1245,8 @@
       <c r="O17" t="str">
         <v/>
       </c>
-      <c r="P17" t="str">
-        <v/>
+      <c r="P17">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1283,8 +1283,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>1</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1309,8 +1309,8 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" t="str">
-        <v/>
+      <c r="D19">
+        <v>2</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1359,8 +1359,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="D20">
+        <v>1</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1409,8 +1409,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1433,8 +1433,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21" t="str">
-        <v/>
+      <c r="L21">
+        <v>3</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1459,8 +1459,8 @@
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22">
-        <v>2</v>
+      <c r="D22" t="str">
+        <v/>
       </c>
       <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -1495,8 +1495,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22">
-        <v>1</v>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1509,8 +1509,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" t="str">
-        <v/>
+      <c r="D23">
+        <v>4</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1545,8 +1545,8 @@
       <c r="O23" t="str">
         <v/>
       </c>
-      <c r="P23" t="str">
-        <v/>
+      <c r="P23">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1595,8 +1595,8 @@
       <c r="O24" t="str">
         <v/>
       </c>
-      <c r="P24">
-        <v>1</v>
+      <c r="P24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1709,8 +1709,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27">
-        <v>1</v>
+      <c r="D27" t="str">
+        <v/>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1845,8 +1845,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29">
-        <v>2</v>
+      <c r="P29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1895,8 +1895,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30" t="str">
-        <v/>
+      <c r="P30">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2009,8 +2009,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="D33">
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2045,8 +2045,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33" t="str">
-        <v/>
+      <c r="P33">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2095,8 +2095,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34">
-        <v>1</v>
+      <c r="P34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2146,7 +2146,7 @@
         <v/>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2159,8 +2159,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36">
-        <v>1</v>
+      <c r="D36" t="str">
+        <v/>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2195,8 +2195,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36">
-        <v>2</v>
+      <c r="P36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2209,8 +2209,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37">
-        <v>2</v>
+      <c r="D37" t="str">
+        <v/>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2309,8 +2309,8 @@
       <c r="C39" t="str">
         <v/>
       </c>
-      <c r="D39">
-        <v>1</v>
+      <c r="D39" t="str">
+        <v/>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2409,8 +2409,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41" t="str">
-        <v/>
+      <c r="D41">
+        <v>1</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2510,7 +2510,7 @@
         <v/>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -471,8 +471,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -484,7 +484,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -495,8 +495,8 @@
       <c r="O2" t="str">
         <v/>
       </c>
-      <c r="P2" t="str">
-        <v/>
+      <c r="P2">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -534,7 +534,7 @@
         <v/>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -545,8 +545,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3">
-        <v>1</v>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -595,8 +595,8 @@
       <c r="O4" t="str">
         <v/>
       </c>
-      <c r="P4">
-        <v>1</v>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -645,8 +645,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5">
-        <v>1</v>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -671,8 +671,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -695,8 +695,8 @@
       <c r="O6" t="str">
         <v/>
       </c>
-      <c r="P6">
-        <v>2</v>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -709,8 +709,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -721,8 +721,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -733,8 +733,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="L7" t="str">
+        <v/>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -745,8 +745,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7">
-        <v>1</v>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -796,7 +796,7 @@
         <v/>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -821,8 +821,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9">
-        <v>1</v>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -871,8 +871,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10">
-        <v>2</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -883,8 +883,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10">
-        <v>1</v>
+      <c r="L10" t="str">
+        <v/>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -959,8 +959,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12">
-        <v>3</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -983,8 +983,8 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12">
-        <v>1</v>
+      <c r="L12" t="str">
+        <v/>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1009,8 +1009,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1021,8 +1021,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13">
-        <v>2</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1159,8 +1159,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16" t="str">
-        <v/>
+      <c r="D16">
+        <v>2</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1209,8 +1209,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17">
-        <v>2</v>
+      <c r="D17" t="str">
+        <v/>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>2</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1359,8 +1359,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20">
-        <v>1</v>
+      <c r="D20" t="str">
+        <v/>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1409,8 +1409,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21">
-        <v>1</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1495,8 +1495,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22" t="str">
-        <v/>
+      <c r="P22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1509,8 +1509,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23">
-        <v>4</v>
+      <c r="D23" t="str">
+        <v/>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>3</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1695,8 +1695,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26">
-        <v>1</v>
+      <c r="P26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1709,8 +1709,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27" t="str">
-        <v/>
+      <c r="D27">
+        <v>2</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1845,8 +1845,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29" t="str">
-        <v/>
+      <c r="P29">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1859,8 +1859,8 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30" t="str">
-        <v/>
+      <c r="D30">
+        <v>2</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1909,8 +1909,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31" t="str">
-        <v/>
+      <c r="D31">
+        <v>1</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1995,8 +1995,8 @@
       <c r="O32" t="str">
         <v/>
       </c>
-      <c r="P32" t="str">
-        <v/>
+      <c r="P32">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2009,8 +2009,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33">
-        <v>1</v>
+      <c r="D33" t="str">
+        <v/>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2109,8 +2109,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2195,8 +2195,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36" t="str">
-        <v/>
+      <c r="P36">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2410,7 +2410,7 @@
         <v/>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -471,8 +471,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -522,7 +522,7 @@
         <v/>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -533,8 +533,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3">
-        <v>3</v>
+      <c r="L3" t="str">
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -545,8 +545,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
-        <v/>
+      <c r="P3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -609,8 +609,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5">
-        <v>2</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -659,8 +659,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -671,8 +671,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6">
-        <v>1</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -695,8 +695,8 @@
       <c r="O6" t="str">
         <v/>
       </c>
-      <c r="P6" t="str">
-        <v/>
+      <c r="P6">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -710,7 +710,7 @@
         <v/>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -759,8 +759,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>2</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -783,8 +783,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8" t="str">
-        <v/>
+      <c r="L8">
+        <v>1</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -796,7 +796,7 @@
         <v/>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -883,8 +883,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10" t="str">
-        <v/>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -921,8 +921,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -959,8 +959,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -983,8 +983,8 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12" t="str">
-        <v/>
+      <c r="L12">
+        <v>4</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1021,8 +1021,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1160,7 +1160,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>2</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1259,8 +1259,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18">
-        <v>1</v>
+      <c r="D18" t="str">
+        <v/>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1283,8 +1283,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18">
-        <v>1</v>
+      <c r="L18" t="str">
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1310,7 +1310,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1383,8 +1383,8 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20" t="str">
-        <v/>
+      <c r="L20">
+        <v>1</v>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1433,8 +1433,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21">
-        <v>2</v>
+      <c r="L21" t="str">
+        <v/>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1483,8 +1483,8 @@
       <c r="K22" t="str">
         <v/>
       </c>
-      <c r="L22" t="str">
-        <v/>
+      <c r="L22">
+        <v>1</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1496,7 +1496,7 @@
         <v/>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1710,7 +1710,7 @@
         <v/>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>1</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1996,7 +1996,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2046,7 +2046,7 @@
         <v/>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2159,8 +2159,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36" t="str">
-        <v/>
+      <c r="D36">
+        <v>1</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2196,7 +2196,7 @@
         <v/>
       </c>
       <c r="P36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2209,8 +2209,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37" t="str">
-        <v/>
+      <c r="D37">
+        <v>1</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2409,8 +2409,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41">
-        <v>2</v>
+      <c r="D41" t="str">
+        <v/>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2445,8 +2445,8 @@
       <c r="O41" t="str">
         <v/>
       </c>
-      <c r="P41" t="str">
-        <v/>
+      <c r="P41">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2509,8 +2509,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43">
-        <v>1</v>
+      <c r="D43" t="str">
+        <v/>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -471,8 +471,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -484,7 +484,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -533,8 +533,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="L3">
+        <v>4</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +572,7 @@
         <v/>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -583,8 +583,8 @@
       <c r="K4" t="str">
         <v/>
       </c>
-      <c r="L4" t="str">
-        <v/>
+      <c r="L4">
+        <v>1</v>
       </c>
       <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
@@ -609,8 +609,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -645,8 +645,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -659,8 +659,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6">
-        <v>2</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -710,7 +710,7 @@
         <v/>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -721,8 +721,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -733,8 +733,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7" t="str">
-        <v/>
+      <c r="L7">
+        <v>1</v>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -745,8 +745,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -933,8 +933,8 @@
       <c r="K11" t="str">
         <v/>
       </c>
-      <c r="L11" t="str">
-        <v/>
+      <c r="L11">
+        <v>1</v>
       </c>
       <c r="M11" t="str">
         <v>COCCO AL RUM</v>
@@ -971,8 +971,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -996,7 +996,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1009,8 +1009,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1021,8 +1021,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13">
-        <v>1</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1183,8 +1183,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16" t="str">
-        <v/>
+      <c r="L16">
+        <v>1</v>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1209,8 +1209,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17" t="str">
-        <v/>
+      <c r="D17">
+        <v>1</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>3</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1259,8 +1259,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" t="str">
-        <v/>
+      <c r="D18">
+        <v>1</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1283,8 +1283,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>2</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1309,8 +1309,8 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19">
-        <v>1</v>
+      <c r="D19" t="str">
+        <v/>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1409,8 +1409,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1433,8 +1433,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21" t="str">
-        <v/>
+      <c r="L21">
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1495,8 +1495,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22">
-        <v>2</v>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1509,8 +1509,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" t="str">
-        <v/>
+      <c r="D23">
+        <v>4</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1559,8 +1559,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" t="str">
-        <v/>
+      <c r="D24">
+        <v>1</v>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1595,8 +1595,8 @@
       <c r="O24" t="str">
         <v/>
       </c>
-      <c r="P24" t="str">
-        <v/>
+      <c r="P24">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1646,7 +1646,7 @@
         <v/>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1695,8 +1695,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26" t="str">
-        <v/>
+      <c r="P26">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1809,8 +1809,8 @@
       <c r="C29" t="str">
         <v/>
       </c>
-      <c r="D29">
-        <v>4</v>
+      <c r="D29" t="str">
+        <v/>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1895,8 +1895,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30">
-        <v>1</v>
+      <c r="P30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1909,8 +1909,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31">
-        <v>1</v>
+      <c r="D31" t="str">
+        <v/>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2009,8 +2009,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="D33">
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2046,7 +2046,7 @@
         <v/>
       </c>
       <c r="P33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2095,8 +2095,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34" t="str">
-        <v/>
+      <c r="P34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2109,8 +2109,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35" t="str">
-        <v/>
+      <c r="D35">
+        <v>2</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2309,8 +2309,8 @@
       <c r="C39" t="str">
         <v/>
       </c>
-      <c r="D39" t="str">
-        <v/>
+      <c r="D39">
+        <v>2</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2509,8 +2509,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43" t="str">
-        <v/>
+      <c r="D43">
+        <v>3</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -471,8 +471,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>2</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -509,8 +509,8 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3">
-        <v>7</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -533,8 +533,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3">
-        <v>4</v>
+      <c r="L3" t="str">
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -545,8 +545,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3">
-        <v>1</v>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -559,8 +559,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>4</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -584,7 +584,7 @@
         <v/>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
@@ -595,8 +595,8 @@
       <c r="O4" t="str">
         <v/>
       </c>
-      <c r="P4" t="str">
-        <v/>
+      <c r="P4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -621,8 +621,8 @@
       <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H5">
-        <v>1</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -645,8 +645,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5">
-        <v>3</v>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -671,8 +671,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -709,8 +709,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7">
-        <v>3</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -733,8 +733,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="L7" t="str">
+        <v/>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -771,8 +771,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8">
-        <v>1</v>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -921,8 +921,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11">
-        <v>1</v>
+      <c r="H11" t="str">
+        <v/>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -933,8 +933,8 @@
       <c r="K11" t="str">
         <v/>
       </c>
-      <c r="L11">
-        <v>1</v>
+      <c r="L11" t="str">
+        <v/>
       </c>
       <c r="M11" t="str">
         <v>COCCO AL RUM</v>
@@ -959,8 +959,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12">
-        <v>3</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -972,7 +972,7 @@
         <v/>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -996,7 +996,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1021,8 +1021,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>3</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1072,7 +1072,7 @@
         <v/>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
         <v>CIOCCOLATO UGANDA</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1160,7 +1160,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1183,8 +1183,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16">
-        <v>1</v>
+      <c r="L16" t="str">
+        <v/>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>3</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1283,8 +1283,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18">
-        <v>2</v>
+      <c r="L18" t="str">
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1333,8 +1333,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19">
-        <v>1</v>
+      <c r="L19" t="str">
+        <v/>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1384,7 +1384,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1409,8 +1409,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21">
-        <v>1</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1483,8 +1483,8 @@
       <c r="K22" t="str">
         <v/>
       </c>
-      <c r="L22">
-        <v>1</v>
+      <c r="L22" t="str">
+        <v/>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1509,8 +1509,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23">
-        <v>4</v>
+      <c r="D23" t="str">
+        <v/>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>2</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1696,7 +1696,7 @@
         <v/>
       </c>
       <c r="P26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1709,8 +1709,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27">
-        <v>1</v>
+      <c r="D27" t="str">
+        <v/>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1846,7 +1846,7 @@
         <v/>
       </c>
       <c r="P29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>1</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1996,7 +1996,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2009,8 +2009,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33">
-        <v>1</v>
+      <c r="D33" t="str">
+        <v/>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2045,8 +2045,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33">
-        <v>3</v>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="P34">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2110,7 +2110,7 @@
         <v/>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2146,7 +2146,7 @@
         <v/>
       </c>
       <c r="P35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2196,7 +2196,7 @@
         <v/>
       </c>
       <c r="P36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2210,7 +2210,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -459,8 +459,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2">
-        <v>3</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -509,8 +509,8 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="D3">
+        <v>8</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -533,8 +533,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -559,8 +559,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>3</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -583,8 +583,8 @@
       <c r="K4" t="str">
         <v/>
       </c>
-      <c r="L4">
-        <v>2</v>
+      <c r="L4" t="str">
+        <v/>
       </c>
       <c r="M4" t="str">
         <v>ANANAS E ZENZERO</v>
@@ -596,7 +596,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -621,8 +621,8 @@
       <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -672,7 +672,7 @@
         <v/>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -709,8 +709,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -721,8 +721,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -760,7 +760,7 @@
         <v/>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -771,8 +771,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>2</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -871,8 +871,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>1</v>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -883,8 +883,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10">
-        <v>1</v>
+      <c r="L10" t="str">
+        <v/>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -895,8 +895,8 @@
       <c r="O10" t="str">
         <v/>
       </c>
-      <c r="P10" t="str">
-        <v/>
+      <c r="P10">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -959,8 +959,8 @@
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1009,8 +1009,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1022,7 +1022,7 @@
         <v/>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1145,8 +1145,8 @@
       <c r="O15" t="str">
         <v/>
       </c>
-      <c r="P15">
-        <v>1</v>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1160,7 +1160,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1260,7 +1260,7 @@
         <v/>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1283,8 +1283,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>2</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1333,8 +1333,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19" t="str">
-        <v/>
+      <c r="L19">
+        <v>2</v>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1409,8 +1409,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>2</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1459,8 +1459,8 @@
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22" t="str">
-        <v/>
+      <c r="D22">
+        <v>2</v>
       </c>
       <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -1495,8 +1495,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22" t="str">
-        <v/>
+      <c r="P22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1509,8 +1509,8 @@
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" t="str">
-        <v/>
+      <c r="D23">
+        <v>3</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1559,8 +1559,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24">
-        <v>2</v>
+      <c r="D24" t="str">
+        <v/>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1696,7 +1696,7 @@
         <v/>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1759,8 +1759,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28">
-        <v>3</v>
+      <c r="D28" t="str">
+        <v/>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1795,8 +1795,8 @@
       <c r="O28" t="str">
         <v/>
       </c>
-      <c r="P28" t="str">
-        <v/>
+      <c r="P28">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1845,8 +1845,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29">
-        <v>2</v>
+      <c r="P29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1995,8 +1995,8 @@
       <c r="O32" t="str">
         <v/>
       </c>
-      <c r="P32">
-        <v>1</v>
+      <c r="P32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -2009,8 +2009,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="D33">
+        <v>3</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2045,8 +2045,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33" t="str">
-        <v/>
+      <c r="P33">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2095,8 +2095,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34">
-        <v>3</v>
+      <c r="P34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2159,8 +2159,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36">
-        <v>1</v>
+      <c r="D36" t="str">
+        <v/>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2195,8 +2195,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36">
-        <v>3</v>
+      <c r="P36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2210,7 +2210,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2259,8 +2259,8 @@
       <c r="C38" t="str">
         <v/>
       </c>
-      <c r="D38">
-        <v>1</v>
+      <c r="D38" t="str">
+        <v/>
       </c>
       <c r="E38" t="str">
         <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
@@ -2345,8 +2345,8 @@
       <c r="O39" t="str">
         <v/>
       </c>
-      <c r="P39" t="str">
-        <v/>
+      <c r="P39">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2409,8 +2409,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41" t="str">
-        <v/>
+      <c r="D41">
+        <v>1</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2495,8 +2495,8 @@
       <c r="O42" t="str">
         <v/>
       </c>
-      <c r="P42">
-        <v>1</v>
+      <c r="P42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2510,7 +2510,7 @@
         <v/>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -459,8 +459,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -471,8 +471,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -484,7 +484,7 @@
         <v/>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -534,7 +534,7 @@
         <v/>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -545,8 +545,8 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
-        <v/>
+      <c r="P3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>3</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -596,7 +596,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -622,7 +622,7 @@
         <v/>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -633,8 +633,8 @@
       <c r="K5" t="str">
         <v/>
       </c>
-      <c r="L5" t="str">
-        <v/>
+      <c r="L5">
+        <v>1</v>
       </c>
       <c r="M5" t="str">
         <v>ANGURIA</v>
@@ -645,8 +645,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -659,8 +659,8 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -709,8 +709,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -721,8 +721,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -759,8 +759,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>2</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -821,8 +821,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>3</v>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -883,8 +883,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10" t="str">
-        <v/>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -921,8 +921,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -971,8 +971,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12">
-        <v>2</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1009,8 +1009,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1021,8 +1021,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13">
-        <v>1</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1033,8 +1033,8 @@
       <c r="K13" t="str">
         <v/>
       </c>
-      <c r="L13" t="str">
-        <v/>
+      <c r="L13">
+        <v>1</v>
       </c>
       <c r="M13" t="str">
         <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1160,7 +1160,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1260,7 +1260,7 @@
         <v/>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1284,7 +1284,7 @@
         <v/>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1333,8 +1333,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19">
-        <v>2</v>
+      <c r="L19" t="str">
+        <v/>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1359,8 +1359,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="D20">
+        <v>2</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1383,8 +1383,8 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20">
-        <v>2</v>
+      <c r="L20" t="str">
+        <v/>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1483,8 +1483,8 @@
       <c r="K22" t="str">
         <v/>
       </c>
-      <c r="L22" t="str">
-        <v/>
+      <c r="L22">
+        <v>1</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1496,7 +1496,7 @@
         <v/>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1510,7 +1510,7 @@
         <v/>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1559,8 +1559,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" t="str">
-        <v/>
+      <c r="D24">
+        <v>1</v>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>3</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1695,8 +1695,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26">
-        <v>3</v>
+      <c r="P26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1709,8 +1709,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27" t="str">
-        <v/>
+      <c r="D27">
+        <v>3</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1759,8 +1759,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28" t="str">
-        <v/>
+      <c r="D28">
+        <v>9</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1795,8 +1795,8 @@
       <c r="O28" t="str">
         <v/>
       </c>
-      <c r="P28">
-        <v>1</v>
+      <c r="P28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1809,8 +1809,8 @@
       <c r="C29" t="str">
         <v/>
       </c>
-      <c r="D29" t="str">
-        <v/>
+      <c r="D29">
+        <v>1</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1859,8 +1859,8 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30">
-        <v>2</v>
+      <c r="D30" t="str">
+        <v/>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1895,8 +1895,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30" t="str">
-        <v/>
+      <c r="P30">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1909,8 +1909,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31" t="str">
-        <v/>
+      <c r="D31">
+        <v>1</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>2</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1995,8 +1995,8 @@
       <c r="O32" t="str">
         <v/>
       </c>
-      <c r="P32" t="str">
-        <v/>
+      <c r="P32">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2010,7 +2010,7 @@
         <v/>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2045,8 +2045,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33">
-        <v>2</v>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2095,8 +2095,8 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34" t="str">
-        <v/>
+      <c r="P34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2109,8 +2109,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2159,8 +2159,8 @@
       <c r="C36" t="str">
         <v/>
       </c>
-      <c r="D36" t="str">
-        <v/>
+      <c r="D36">
+        <v>1</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2210,7 +2210,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2410,7 +2410,7 @@
         <v/>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="P41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -459,8 +459,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2">
-        <v>5</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -471,8 +471,8 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2">
-        <v>2</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>CIOCCOLATO</v>
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -533,8 +533,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3">
-        <v>5</v>
+      <c r="L3" t="str">
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -596,7 +596,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -609,8 +609,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5">
-        <v>3</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -622,7 +622,7 @@
         <v/>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -645,8 +645,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5">
-        <v>4</v>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -671,8 +671,8 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6">
-        <v>2</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -696,7 +696,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -709,8 +709,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>2</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -721,8 +721,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -745,8 +745,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7">
-        <v>3</v>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -759,8 +759,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>4</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -783,8 +783,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8">
-        <v>4</v>
+      <c r="L8" t="str">
+        <v/>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -821,8 +821,8 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9">
-        <v>3</v>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -909,8 +909,8 @@
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11">
-        <v>1</v>
+      <c r="D11" t="str">
+        <v/>
       </c>
       <c r="E11" t="str">
         <v>LEMON CURD</v>
@@ -922,7 +922,7 @@
         <v/>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -960,7 +960,7 @@
         <v/>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1160,7 +1160,7 @@
         <v/>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1183,8 +1183,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16" t="str">
-        <v/>
+      <c r="L16">
+        <v>1</v>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>3</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1309,8 +1309,8 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" t="str">
-        <v/>
+      <c r="D19">
+        <v>1</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1333,8 +1333,8 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19" t="str">
-        <v/>
+      <c r="L19">
+        <v>2</v>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1359,8 +1359,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20">
-        <v>2</v>
+      <c r="D20" t="str">
+        <v/>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1409,8 +1409,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21">
-        <v>2</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1495,8 +1495,8 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22">
-        <v>3</v>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1510,7 +1510,7 @@
         <v/>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1710,7 +1710,7 @@
         <v/>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1845,8 +1845,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29" t="str">
-        <v/>
+      <c r="P29">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1910,7 +1910,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1996,7 +1996,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2010,7 +2010,7 @@
         <v/>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2109,8 +2109,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35" t="str">
-        <v/>
+      <c r="D35">
+        <v>1</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2209,8 +2209,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37">
-        <v>2</v>
+      <c r="D37" t="str">
+        <v/>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2345,8 +2345,8 @@
       <c r="O39" t="str">
         <v/>
       </c>
-      <c r="P39">
-        <v>2</v>
+      <c r="P39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2445,8 +2445,8 @@
       <c r="O41" t="str">
         <v/>
       </c>
-      <c r="P41">
-        <v>2</v>
+      <c r="P41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2509,8 +2509,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43">
-        <v>1</v>
+      <c r="D43" t="str">
+        <v/>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -459,8 +459,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3">
-        <v>3</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -533,8 +533,8 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -559,8 +559,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4">
-        <v>3</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4">
-        <v>4</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -609,8 +609,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -621,8 +621,8 @@
       <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H5">
-        <v>2</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -660,7 +660,7 @@
         <v/>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -696,7 +696,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -709,8 +709,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7">
-        <v>2</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -745,8 +745,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -759,8 +759,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>4</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -783,8 +783,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8" t="str">
-        <v/>
+      <c r="L8">
+        <v>3</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -922,7 +922,7 @@
         <v/>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -971,8 +971,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>3</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -995,8 +995,8 @@
       <c r="O12" t="str">
         <v/>
       </c>
-      <c r="P12">
-        <v>1</v>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1133,8 +1133,8 @@
       <c r="K15" t="str">
         <v/>
       </c>
-      <c r="L15">
-        <v>4</v>
+      <c r="L15" t="str">
+        <v/>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1159,8 +1159,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16">
-        <v>4</v>
+      <c r="D16" t="str">
+        <v/>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1210,7 +1210,7 @@
         <v/>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17">
-        <v>3</v>
+      <c r="L17" t="str">
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1259,8 +1259,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18">
-        <v>1</v>
+      <c r="D18" t="str">
+        <v/>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1283,8 +1283,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18">
-        <v>1</v>
+      <c r="L18" t="str">
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1310,7 +1310,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1409,8 +1409,8 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1559,8 +1559,8 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24">
-        <v>1</v>
+      <c r="D24" t="str">
+        <v/>
       </c>
       <c r="E24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>6</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1709,8 +1709,8 @@
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27">
-        <v>2</v>
+      <c r="D27" t="str">
+        <v/>
       </c>
       <c r="E27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1759,8 +1759,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28">
-        <v>2</v>
+      <c r="D28" t="str">
+        <v/>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1896,7 +1896,7 @@
         <v/>
       </c>
       <c r="P30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1910,7 +1910,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1996,7 +1996,7 @@
         <v/>
       </c>
       <c r="P32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="P34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2109,8 +2109,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2146,7 +2146,7 @@
         <v/>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2195,8 +2195,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36" t="str">
-        <v/>
+      <c r="P36">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2209,8 +2209,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37" t="str">
-        <v/>
+      <c r="D37">
+        <v>1</v>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -2509,8 +2509,8 @@
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43" t="str">
-        <v/>
+      <c r="D43">
+        <v>2</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -459,8 +459,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -483,8 +483,8 @@
       <c r="K2" t="str">
         <v/>
       </c>
-      <c r="L2">
-        <v>1</v>
+      <c r="L2" t="str">
+        <v/>
       </c>
       <c r="M2" t="str">
         <v>ALBICOCCA</v>
@@ -510,7 +510,7 @@
         <v/>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -534,7 +534,7 @@
         <v/>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="str">
         <v>AMARENA</v>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -609,8 +609,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5">
-        <v>3</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -660,7 +660,7 @@
         <v/>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -696,7 +696,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -709,8 +709,8 @@
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -733,8 +733,8 @@
       <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L7" t="str">
-        <v/>
+      <c r="L7">
+        <v>2</v>
       </c>
       <c r="M7" t="str">
         <v>BANANA E LIME</v>
@@ -745,8 +745,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7">
-        <v>1</v>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -759,8 +759,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>4</v>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -771,8 +771,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8">
-        <v>1</v>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -795,8 +795,8 @@
       <c r="O8" t="str">
         <v/>
       </c>
-      <c r="P8">
-        <v>1</v>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -883,8 +883,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10">
-        <v>1</v>
+      <c r="L10" t="str">
+        <v/>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -960,7 +960,7 @@
         <v/>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -971,8 +971,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12">
-        <v>3</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -983,8 +983,8 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12">
-        <v>4</v>
+      <c r="L12" t="str">
+        <v/>
       </c>
       <c r="M12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -1009,8 +1009,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1021,8 +1021,8 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>2</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1133,8 +1133,8 @@
       <c r="K15" t="str">
         <v/>
       </c>
-      <c r="L15" t="str">
-        <v/>
+      <c r="L15">
+        <v>1</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1159,8 +1159,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16" t="str">
-        <v/>
+      <c r="D16">
+        <v>4</v>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1210,7 +1210,7 @@
         <v/>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1283,8 +1283,8 @@
       <c r="K18" t="str">
         <v/>
       </c>
-      <c r="L18" t="str">
-        <v/>
+      <c r="L18">
+        <v>1</v>
       </c>
       <c r="M18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -1310,7 +1310,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -1359,8 +1359,8 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="D20">
+        <v>1</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1433,8 +1433,8 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21">
-        <v>2</v>
+      <c r="L21" t="str">
+        <v/>
       </c>
       <c r="M21" t="str">
         <v>HIBISCUS</v>
@@ -1460,7 +1460,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
-        <v/>
+      <c r="P25">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1759,8 +1759,8 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28" t="str">
-        <v/>
+      <c r="D28">
+        <v>3</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1795,8 +1795,8 @@
       <c r="O28" t="str">
         <v/>
       </c>
-      <c r="P28" t="str">
-        <v/>
+      <c r="P28">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1846,7 +1846,7 @@
         <v/>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1895,8 +1895,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30">
-        <v>2</v>
+      <c r="P30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
-        <v/>
+      <c r="P31">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2010,7 +2010,7 @@
         <v/>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -2045,8 +2045,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33" t="str">
-        <v/>
+      <c r="P33">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2109,8 +2109,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35" t="str">
-        <v/>
+      <c r="D35">
+        <v>2</v>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2160,7 +2160,7 @@
         <v/>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2196,7 +2196,7 @@
         <v/>
       </c>
       <c r="P36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2410,7 +2410,7 @@
         <v/>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2459,8 +2459,8 @@
       <c r="C42" t="str">
         <v/>
       </c>
-      <c r="D42" t="str">
-        <v/>
+      <c r="D42">
+        <v>1</v>
       </c>
       <c r="E42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -459,8 +459,8 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2" t="str">
         <v>CARROT CAKE</v>
@@ -495,8 +495,8 @@
       <c r="O2" t="str">
         <v/>
       </c>
-      <c r="P2">
-        <v>1</v>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -509,8 +509,8 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3">
-        <v>8</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -521,8 +521,8 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -559,8 +559,8 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>3</v>
       </c>
       <c r="E4" t="str">
         <v>CREMA AGNESE</v>
@@ -571,8 +571,8 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -595,8 +595,8 @@
       <c r="O4" t="str">
         <v/>
       </c>
-      <c r="P4">
-        <v>2</v>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -609,8 +609,8 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>4</v>
       </c>
       <c r="E5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -645,8 +645,8 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
-        <v/>
+      <c r="P5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v/>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>CREMA CANNELLA</v>
@@ -710,7 +710,7 @@
         <v/>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -721,8 +721,8 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7">
-        <v>2</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -745,8 +745,8 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7" t="str">
-        <v/>
+      <c r="P7">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -759,8 +759,8 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>4</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -771,8 +771,8 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>3</v>
       </c>
       <c r="I8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -783,8 +783,8 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8">
-        <v>1</v>
+      <c r="L8" t="str">
+        <v/>
       </c>
       <c r="M8" t="str">
         <v>CACHI</v>
@@ -871,8 +871,8 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10">
-        <v>2</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -883,8 +883,8 @@
       <c r="K10" t="str">
         <v/>
       </c>
-      <c r="L10" t="str">
-        <v/>
+      <c r="L10">
+        <v>1</v>
       </c>
       <c r="M10" t="str">
         <v>COCCO</v>
@@ -921,8 +921,8 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11">
-        <v>1</v>
+      <c r="H11" t="str">
+        <v/>
       </c>
       <c r="I11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -960,7 +960,7 @@
         <v/>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="str">
         <v>SACRIPANTE</v>
@@ -971,8 +971,8 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>4</v>
       </c>
       <c r="I12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -995,8 +995,8 @@
       <c r="O12" t="str">
         <v/>
       </c>
-      <c r="P12" t="str">
-        <v/>
+      <c r="P12">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1009,8 +1009,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>TIRAMISU'</v>
@@ -1022,7 +1022,7 @@
         <v/>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -1134,7 +1134,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M15" t="str">
         <v>FICHI</v>
@@ -1159,8 +1159,8 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16">
-        <v>4</v>
+      <c r="D16" t="str">
+        <v/>
       </c>
       <c r="E16" t="str">
         <v>speciali</v>
@@ -1183,8 +1183,8 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16">
-        <v>1</v>
+      <c r="L16" t="str">
+        <v/>
       </c>
       <c r="M16" t="str">
         <v>FICHI D INDIA</v>
@@ -1209,8 +1209,8 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17">
-        <v>1</v>
+      <c r="D17" t="str">
+        <v/>
       </c>
       <c r="E17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -1233,8 +1233,8 @@
       <c r="K17" t="str">
         <v/>
       </c>
-      <c r="L17" t="str">
-        <v/>
+      <c r="L17">
+        <v>3</v>
       </c>
       <c r="M17" t="str">
         <v>FRAGOLA</v>
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1259,8 +1259,8 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" t="str">
-        <v/>
+      <c r="D18">
+        <v>1</v>
       </c>
       <c r="E18" t="str">
         <v>CASTAGNACCIO</v>
@@ -1295,8 +1295,8 @@
       <c r="O18" t="str">
         <v/>
       </c>
-      <c r="P18" t="str">
-        <v/>
+      <c r="P18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1310,7 +1310,7 @@
         <v/>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="str">
         <v>COTOGNATA</v>
@@ -1360,7 +1360,7 @@
         <v/>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -1383,8 +1383,8 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20" t="str">
-        <v/>
+      <c r="L20">
+        <v>1</v>
       </c>
       <c r="M20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -1510,7 +1510,7 @@
         <v/>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1645,8 +1645,8 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
-        <v>6</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1695,8 +1695,8 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26" t="str">
-        <v/>
+      <c r="P26">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1745,8 +1745,8 @@
       <c r="O27" t="str">
         <v/>
       </c>
-      <c r="P27" t="str">
-        <v/>
+      <c r="P27">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E28" t="str">
         <v>MATE-LATE</v>
@@ -1809,8 +1809,8 @@
       <c r="C29" t="str">
         <v/>
       </c>
-      <c r="D29">
-        <v>5</v>
+      <c r="D29" t="str">
+        <v/>
       </c>
       <c r="E29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1845,8 +1845,8 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29">
-        <v>1</v>
+      <c r="P29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1859,8 +1859,8 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30" t="str">
-        <v/>
+      <c r="D30">
+        <v>3</v>
       </c>
       <c r="E30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1895,8 +1895,8 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30" t="str">
-        <v/>
+      <c r="P30">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1909,8 +1909,8 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31">
-        <v>2</v>
+      <c r="D31" t="str">
+        <v/>
       </c>
       <c r="E31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1945,8 +1945,8 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
-        <v>2</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -2045,8 +2045,8 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33">
-        <v>2</v>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2109,8 +2109,8 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>2</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -2160,7 +2160,7 @@
         <v/>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -2195,8 +2195,8 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36">
-        <v>3</v>
+      <c r="P36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2209,8 +2209,8 @@
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37">
-        <v>1</v>
+      <c r="D37" t="str">
+        <v/>
       </c>
       <c r="E37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -2345,8 +2345,8 @@
       <c r="O39" t="str">
         <v/>
       </c>
-      <c r="P39" t="str">
-        <v/>
+      <c r="P39">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -2409,8 +2409,8 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41">
-        <v>1</v>
+      <c r="D41" t="str">
+        <v/>
       </c>
       <c r="E41" t="str">
         <v>TORRONE SALATO</v>
@@ -2460,7 +2460,7 @@
         <v/>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
@@ -2510,7 +2510,7 @@
         <v/>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -430,7 +430,7 @@
         <v>ARACHIDI</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
@@ -442,7 +442,7 @@
         <v>C. AL LATTE GELATO</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
@@ -456,13 +456,13 @@
         <v>BACIO</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>C. AL PIMENTO</v>
@@ -482,13 +482,13 @@
         <v>BASILICO</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="str">
         <v>C. AGNESE</v>
       </c>
-      <c r="D4">
-        <v>4</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>C. AL WHISKY</v>
@@ -507,14 +507,14 @@
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5">
-        <v>4</v>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
         <v>C. CANNELLA</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5" t="str">
         <v>C. BIANCO</v>
@@ -525,8 +525,8 @@
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5">
-        <v>4</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -539,8 +539,8 @@
       <c r="C6" t="str">
         <v>C. FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D6">
-        <v>2</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
         <v>C. CRUDO DEL PERU'</v>
@@ -552,7 +552,7 @@
         <v>AVOCADO</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -560,25 +560,25 @@
         <v>CAFFE'</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>C. PASTICCIERA PARISI</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>C. E ARANCIA</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
+      <c r="F7">
+        <v>2</v>
       </c>
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7">
-        <v>3</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -624,7 +624,7 @@
         <v>C. KENTUCKY</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -638,7 +638,7 @@
         <v>FIORDILATTE</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C10" t="str">
         <v>LEMON CURD</v>
@@ -655,8 +655,8 @@
       <c r="G10" t="str">
         <v>FRAGOLA</v>
       </c>
-      <c r="H10">
-        <v>6</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -696,7 +696,7 @@
         <v>TIRAMISU'</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>C. ROSEMARY</v>
@@ -708,21 +708,21 @@
         <v>LAMPONI SORBETTO</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>MENTA E C.</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>3</v>
       </c>
       <c r="C13" t="str">
         <v>ZABAIONE GELATO</v>
       </c>
-      <c r="D13">
-        <v>1</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>C. UGANDA</v>
@@ -733,28 +733,28 @@
       <c r="G13" t="str">
         <v>LIMONE</v>
       </c>
-      <c r="H13">
-        <v>2</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
         <v>LIQUIRIZIA</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>1</v>
       </c>
       <c r="E14" t="str">
         <v>C. VENEZUELA</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G14" t="str">
         <v>MANGO</v>
       </c>
-      <c r="H14" t="str">
-        <v/>
+      <c r="H14">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -767,14 +767,14 @@
       <c r="E15" t="str">
         <v>C. WASABI</v>
       </c>
-      <c r="F15" t="str">
-        <v/>
+      <c r="F15">
+        <v>1</v>
       </c>
       <c r="G15" t="str">
         <v>MELA M.C.</v>
       </c>
-      <c r="H15">
-        <v>4</v>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -782,19 +782,19 @@
         <v>MANDORLA BIANCA</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="str">
         <v>ESTASI</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" t="str">
         <v>MELOGRANO</v>
       </c>
-      <c r="H16">
-        <v>4</v>
+      <c r="H16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -817,7 +817,7 @@
         <v>MELONE</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -825,7 +825,7 @@
         <v>MANDORLA TOSTATA</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="str">
         <v>CAPRESE</v>
@@ -869,7 +869,7 @@
         <v>MORA</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -877,7 +877,7 @@
         <v>NOCCIOLA</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C20" t="str">
         <v>CIOCCOLATA CALDA</v>
@@ -889,21 +889,21 @@
         <v>MOU LATTE SALATO</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="str">
         <v>PANACEA</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v>NOCCIOLA BURRO</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>COPPETTA GRANDE</v>
@@ -920,8 +920,8 @@
       <c r="G21" t="str">
         <v>PAPAYA</v>
       </c>
-      <c r="H21">
-        <v>1</v>
+      <c r="H21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -941,15 +941,15 @@
         <v>PASSION FRUIT</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v>PEREBH</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>1</v>
       </c>
       <c r="C23" t="str">
         <v>MOUSSE</v>
@@ -969,7 +969,7 @@
         <v>P.BRONTE</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C24" t="str">
         <v>SUSHI GELATO</v>
@@ -981,7 +981,7 @@
         <v>PERA</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1021,7 +1021,7 @@
         <v>PUNCH PARADISE</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1029,7 +1029,7 @@
         <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="str">
         <v>TORTA CHEESCAKE 6P</v>
@@ -1129,7 +1129,7 @@
         <v>RISO E VANIGLIA</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="str">
         <v>TORTA TIRAMISU 8P</v>
@@ -1141,7 +1141,7 @@
         <v>V. CASTAGNA E MIRTO</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1162,8 +1162,8 @@
       <c r="A34" t="str">
         <v>STRACCHINO PERA</v>
       </c>
-      <c r="B34" t="str">
-        <v/>
+      <c r="B34">
+        <v>1</v>
       </c>
       <c r="G34" t="str">
         <v>V. NOCCIOLA F.</v>
@@ -1185,7 +1185,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C36" t="str">
         <v>TOTAL:</v>
@@ -1203,8 +1203,8 @@
       <c r="A38" t="str">
         <v>VENERE ROSA</v>
       </c>
-      <c r="B38">
-        <v>1</v>
+      <c r="B38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1212,7 +1212,7 @@
         <v>YOGURT</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_template_filled.xlsx
+++ b/output/shocapp_template_filled.xlsx
@@ -442,7 +442,7 @@
         <v>C. AL LATTE GELATO</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
@@ -456,13 +456,13 @@
         <v>BACIO</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="str">
         <v>C. AL PIMENTO</v>
@@ -513,8 +513,8 @@
       <c r="C5" t="str">
         <v>C. CANNELLA</v>
       </c>
-      <c r="D5">
-        <v>1</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>C. BIANCO</v>
@@ -534,13 +534,13 @@
         <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>C. FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6" t="str">
         <v>C. CRUDO DEL PERU'</v>
@@ -552,7 +552,7 @@
         <v>AVOCADO</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -585,14 +585,14 @@
       <c r="A8" t="str">
         <v>COCCO C.</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>C. VANIGLIA</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>1</v>
       </c>
       <c r="E8" t="str">
         <v>C. EQUADOR</v>
@@ -630,7 +630,7 @@
         <v>COCONUT RICE CAKE</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         <v>FIORDILATTE</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="str">
         <v>LEMON CURD</v>
@@ -655,8 +655,8 @@
       <c r="G10" t="str">
         <v>FRAGOLA</v>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         <v>SACRIPANTE</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="str">
         <v>C. MADAGASCAR</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
+      <c r="F11">
+        <v>2</v>
       </c>
       <c r="G11" t="str">
         <v>FRUTTI DI BOSCO</v>
@@ -708,7 +708,7 @@
         <v>LAMPONI SORBETTO</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -727,14 +727,14 @@
       <c r="E13" t="str">
         <v>C. UGANDA</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
+      <c r="F13">
+        <v>1</v>
       </c>
       <c r="G13" t="str">
         <v>LIMONE</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -754,7 +754,7 @@
         <v>MANGO</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -773,8 +773,8 @@
       <c r="G15" t="str">
         <v>MELA M.C.</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="H15">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -802,7 +802,7 @@
         <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="str">
         <v>Varie</v>
@@ -863,7 +863,7 @@
         <v>V. GIANDUIA VARIEGATA</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" t="str">
         <v>MORA</v>
@@ -877,7 +877,7 @@
         <v>NOCCIOLA</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" t="str">
         <v>CIOCCOLATA CALDA</v>
@@ -889,7 +889,7 @@
         <v>MOU LATTE SALATO</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" t="str">
         <v>PANACEA</v>
@@ -941,7 +941,7 @@
         <v>PASSION FRUIT</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -961,7 +961,7 @@
         <v>PENSIERO</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1021,7 +1021,7 @@
         <v>PUNCH PARADISE</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1101,7 +1101,7 @@
         <v>V. BANACHI</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1148,8 +1148,8 @@
       <c r="A33" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>1</v>
       </c>
       <c r="G33" t="str">
         <v>V.BRONTE GREEN</v>
@@ -1176,8 +1176,8 @@
       <c r="A35" t="str">
         <v>STRACCHINO ALBICOCCHA</v>
       </c>
-      <c r="B35">
-        <v>1</v>
+      <c r="B35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1185,7 +1185,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="str">
         <v>TOTAL:</v>
